--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/51.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/51.xlsx
@@ -426,13 +426,13 @@
         <v>-2.946028070658183</v>
       </c>
       <c r="E2">
-        <v>-7.536628155823186</v>
+        <v>-8.889840344217266</v>
       </c>
       <c r="F2">
-        <v>-7.068610687117255</v>
+        <v>-7.491241219196779</v>
       </c>
       <c r="G2">
-        <v>-8.793938999001497</v>
+        <v>-11.06189112104447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.171612968726252</v>
       </c>
       <c r="E3">
-        <v>-7.179413069150133</v>
+        <v>-9.477821937847192</v>
       </c>
       <c r="F3">
-        <v>-7.056316378095699</v>
+        <v>-6.633529850983505</v>
       </c>
       <c r="G3">
-        <v>-8.19356494436359</v>
+        <v>-10.28286347637979</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.500634103000599</v>
       </c>
       <c r="E4">
-        <v>-8.322898040826974</v>
+        <v>-8.988737688070778</v>
       </c>
       <c r="F4">
-        <v>-6.857839622022687</v>
+        <v>-6.843508667193875</v>
       </c>
       <c r="G4">
-        <v>-9.040541536221809</v>
+        <v>-11.25872622717292</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.04522420520337</v>
       </c>
       <c r="E5">
-        <v>-7.869534394023065</v>
+        <v>-8.288182759084174</v>
       </c>
       <c r="F5">
-        <v>-7.200225754999288</v>
+        <v>-6.962003523419449</v>
       </c>
       <c r="G5">
-        <v>-9.291361708459151</v>
+        <v>-11.50542477021387</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.7709032657267384</v>
       </c>
       <c r="E6">
-        <v>-8.608037935193947</v>
+        <v>-9.550073740639572</v>
       </c>
       <c r="F6">
-        <v>-6.850127766067454</v>
+        <v>-6.654278378108156</v>
       </c>
       <c r="G6">
-        <v>-8.820681585867732</v>
+        <v>-12.16886140682935</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.6674203076075935</v>
       </c>
       <c r="E7">
-        <v>-9.581854571225403</v>
+        <v>-10.5672686291905</v>
       </c>
       <c r="F7">
-        <v>-6.675270400017307</v>
+        <v>-6.551412323709097</v>
       </c>
       <c r="G7">
-        <v>-9.248390827359412</v>
+        <v>-11.60725715100185</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.686647028688536</v>
       </c>
       <c r="E8">
-        <v>-10.22542771177349</v>
+        <v>-12.13936460874533</v>
       </c>
       <c r="F8">
-        <v>-6.909269283847146</v>
+        <v>-6.507803397621556</v>
       </c>
       <c r="G8">
-        <v>-9.62527988427774</v>
+        <v>-11.92100417284966</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.7853574257598034</v>
       </c>
       <c r="E9">
-        <v>-11.503326848946</v>
+        <v>-11.66737534834787</v>
       </c>
       <c r="F9">
-        <v>-6.732842861161276</v>
+        <v>-6.229672568825602</v>
       </c>
       <c r="G9">
-        <v>-10.14036104364187</v>
+        <v>-12.64490130264885</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.906511485415182</v>
       </c>
       <c r="E10">
-        <v>-11.8399011510921</v>
+        <v>-13.17080154805038</v>
       </c>
       <c r="F10">
-        <v>-6.486621331002554</v>
+        <v>-6.585549896569352</v>
       </c>
       <c r="G10">
-        <v>-9.789883519035842</v>
+        <v>-12.45868973715593</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.003172258411861</v>
       </c>
       <c r="E11">
-        <v>-12.38768348095593</v>
+        <v>-12.36557547085049</v>
       </c>
       <c r="F11">
-        <v>-6.283861046354756</v>
+        <v>-6.51016351536204</v>
       </c>
       <c r="G11">
-        <v>-10.4729682434269</v>
+        <v>-12.69499978829464</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.038650541859912</v>
       </c>
       <c r="E12">
-        <v>-13.61571053388197</v>
+        <v>-14.30704548978896</v>
       </c>
       <c r="F12">
-        <v>-5.899621921224359</v>
+        <v>-6.911929909785084</v>
       </c>
       <c r="G12">
-        <v>-9.460927850980621</v>
+        <v>-12.9973452913052</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.9916368775540804</v>
       </c>
       <c r="E13">
-        <v>-13.22533343205075</v>
+        <v>-13.1848624598442</v>
       </c>
       <c r="F13">
-        <v>-6.051621263870491</v>
+        <v>-6.35571180410585</v>
       </c>
       <c r="G13">
-        <v>-9.648814552516418</v>
+        <v>-12.50526580234793</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.8597582943812045</v>
       </c>
       <c r="E14">
-        <v>-13.66507090056558</v>
+        <v>-15.66708661698661</v>
       </c>
       <c r="F14">
-        <v>-5.84279934483135</v>
+        <v>-6.513779115966988</v>
       </c>
       <c r="G14">
-        <v>-9.115085090129579</v>
+        <v>-11.8338507509828</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.6542128362584707</v>
       </c>
       <c r="E15">
-        <v>-14.10776999108143</v>
+        <v>-15.35765598804249</v>
       </c>
       <c r="F15">
-        <v>-5.978599751521409</v>
+        <v>-6.266374953415911</v>
       </c>
       <c r="G15">
-        <v>-8.56671970591362</v>
+        <v>-12.01611283564738</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.4004596655840039</v>
       </c>
       <c r="E16">
-        <v>-15.04254665269276</v>
+        <v>-16.51319122905375</v>
       </c>
       <c r="F16">
-        <v>-5.647677273813716</v>
+        <v>-5.868749158108782</v>
       </c>
       <c r="G16">
-        <v>-8.892791888804135</v>
+        <v>-11.46764151397416</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.133814896632214</v>
       </c>
       <c r="E17">
-        <v>-15.4204206377888</v>
+        <v>-16.21358738870627</v>
       </c>
       <c r="F17">
-        <v>-5.318363841316111</v>
+        <v>-5.64805815508638</v>
       </c>
       <c r="G17">
-        <v>-8.597739517616592</v>
+        <v>-10.93035983622369</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1072788848744381</v>
       </c>
       <c r="E18">
-        <v>-16.3388812075505</v>
+        <v>-17.28573078086628</v>
       </c>
       <c r="F18">
-        <v>-5.318627528351032</v>
+        <v>-5.815110622458763</v>
       </c>
       <c r="G18">
-        <v>-8.468138280845203</v>
+        <v>-10.35910202960367</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2856271779630552</v>
       </c>
       <c r="E19">
-        <v>-18.48444955001467</v>
+        <v>-18.417337565221</v>
       </c>
       <c r="F19">
-        <v>-4.948400637233964</v>
+        <v>-5.54724102021542</v>
       </c>
       <c r="G19">
-        <v>-7.570682490604177</v>
+        <v>-10.64867875846926</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.373977768538123</v>
       </c>
       <c r="E20">
-        <v>-16.99450461743299</v>
+        <v>-18.27640239715428</v>
       </c>
       <c r="F20">
-        <v>-4.690437115491694</v>
+        <v>-5.911815664920285</v>
       </c>
       <c r="G20">
-        <v>-7.208389628968495</v>
+        <v>-9.73711342313986</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.3534837310054252</v>
       </c>
       <c r="E21">
-        <v>-19.29035489831572</v>
+        <v>-20.2506630963823</v>
       </c>
       <c r="F21">
-        <v>-4.54240416431078</v>
+        <v>-5.04550318988026</v>
       </c>
       <c r="G21">
-        <v>-6.912456652667505</v>
+        <v>-10.41305399025717</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2199112516705402</v>
       </c>
       <c r="E22">
-        <v>-17.70797022581547</v>
+        <v>-19.79201019193743</v>
       </c>
       <c r="F22">
-        <v>-4.018559383102001</v>
+        <v>-4.694058259067346</v>
       </c>
       <c r="G22">
-        <v>-7.426130830177439</v>
+        <v>-8.802658975951939</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.01839899083265236</v>
       </c>
       <c r="E23">
-        <v>-19.26392672400696</v>
+        <v>-22.10195761240603</v>
       </c>
       <c r="F23">
-        <v>-4.172716525057919</v>
+        <v>-4.499495236237864</v>
       </c>
       <c r="G23">
-        <v>-6.107408120064155</v>
+        <v>-10.13544157297051</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.3428806586953883</v>
       </c>
       <c r="E24">
-        <v>-20.03831842168863</v>
+        <v>-22.59679755264619</v>
       </c>
       <c r="F24">
-        <v>-3.930948771859891</v>
+        <v>-4.555963854358772</v>
       </c>
       <c r="G24">
-        <v>-7.388479995759308</v>
+        <v>-9.145168017444936</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.7232537032680784</v>
       </c>
       <c r="E25">
-        <v>-19.94540772047326</v>
+        <v>-20.57321271452663</v>
       </c>
       <c r="F25">
-        <v>-3.630839668295946</v>
+        <v>-3.961205473374361</v>
       </c>
       <c r="G25">
-        <v>-7.335640378407001</v>
+        <v>-10.08636604589635</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.126267743280962</v>
       </c>
       <c r="E26">
-        <v>-19.52498419360114</v>
+        <v>-21.64543309074477</v>
       </c>
       <c r="F26">
-        <v>-3.664693757797338</v>
+        <v>-4.531300802137634</v>
       </c>
       <c r="G26">
-        <v>-7.496973194172304</v>
+        <v>-10.62488586767852</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.515350366114694</v>
       </c>
       <c r="E27">
-        <v>-21.02998177378431</v>
+        <v>-21.69196316117358</v>
       </c>
       <c r="F27">
-        <v>-3.716302774316721</v>
+        <v>-3.946609247804714</v>
       </c>
       <c r="G27">
-        <v>-8.301657566766334</v>
+        <v>-9.940596104711164</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.856593907413756</v>
       </c>
       <c r="E28">
-        <v>-20.82039946823532</v>
+        <v>-21.49799956247704</v>
       </c>
       <c r="F28">
-        <v>-3.316702889585997</v>
+        <v>-3.883987140349365</v>
       </c>
       <c r="G28">
-        <v>-8.109242038932813</v>
+        <v>-10.39794466041594</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.120445847954679</v>
       </c>
       <c r="E29">
-        <v>-19.59151200524783</v>
+        <v>-22.00780610931256</v>
       </c>
       <c r="F29">
-        <v>-3.571890174858501</v>
+        <v>-4.022121137705824</v>
       </c>
       <c r="G29">
-        <v>-7.758529465593503</v>
+        <v>-10.39958006991234</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.285059484154902</v>
       </c>
       <c r="E30">
-        <v>-19.97729723443527</v>
+        <v>-18.76355751700343</v>
       </c>
       <c r="F30">
-        <v>-3.604200942945297</v>
+        <v>-3.752815114197177</v>
       </c>
       <c r="G30">
-        <v>-8.156192195770757</v>
+        <v>-10.17855811807398</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.335558353221027</v>
       </c>
       <c r="E31">
-        <v>-20.5568377525149</v>
+        <v>-20.71512603297901</v>
       </c>
       <c r="F31">
-        <v>-3.577224096381701</v>
+        <v>-3.87167145129795</v>
       </c>
       <c r="G31">
-        <v>-7.865526297422747</v>
+        <v>-11.22798450129525</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.266769546551801</v>
       </c>
       <c r="E32">
-        <v>-18.97061746253015</v>
+        <v>-21.19858138956389</v>
       </c>
       <c r="F32">
-        <v>-3.089076046506928</v>
+        <v>-4.060039808439191</v>
       </c>
       <c r="G32">
-        <v>-8.326211883031108</v>
+        <v>-9.655770008694427</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.079950774172673</v>
       </c>
       <c r="E33">
-        <v>-19.54519930157138</v>
+        <v>-21.30355141706169</v>
       </c>
       <c r="F33">
-        <v>-3.906774292913665</v>
+        <v>-4.230258103936538</v>
       </c>
       <c r="G33">
-        <v>-7.802016791797369</v>
+        <v>-9.528943009084948</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.782792577398703</v>
       </c>
       <c r="E34">
-        <v>-20.31638483965562</v>
+        <v>-21.62932078022548</v>
       </c>
       <c r="F34">
-        <v>-3.416591972790509</v>
+        <v>-4.056201697153123</v>
       </c>
       <c r="G34">
-        <v>-7.811286319307328</v>
+        <v>-10.38255724474941</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.38925882470079</v>
       </c>
       <c r="E35">
-        <v>-19.46144064632551</v>
+        <v>-19.4238905398539</v>
       </c>
       <c r="F35">
-        <v>-3.236496103498566</v>
+        <v>-4.249111331006887</v>
       </c>
       <c r="G35">
-        <v>-7.815381464139406</v>
+        <v>-9.292672684492702</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9120934204084815</v>
       </c>
       <c r="E36">
-        <v>-17.97166326728211</v>
+        <v>-20.70871371378415</v>
       </c>
       <c r="F36">
-        <v>-3.560056724258338</v>
+        <v>-4.772028060549219</v>
       </c>
       <c r="G36">
-        <v>-7.052658256255639</v>
+        <v>-8.613196454739448</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.369955434166084</v>
       </c>
       <c r="E37">
-        <v>-19.01226583797869</v>
+        <v>-20.1898547474073</v>
       </c>
       <c r="F37">
-        <v>-3.758560799258391</v>
+        <v>-3.662524872546143</v>
       </c>
       <c r="G37">
-        <v>-7.866754509817817</v>
+        <v>-9.655111210132112</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2218285802000816</v>
       </c>
       <c r="E38">
-        <v>-18.0959336510006</v>
+        <v>-21.07801982605768</v>
       </c>
       <c r="F38">
-        <v>-3.393697920076916</v>
+        <v>-3.727310322281983</v>
       </c>
       <c r="G38">
-        <v>-7.076795443782466</v>
+        <v>-9.093384464119655</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.8441092553411059</v>
       </c>
       <c r="E39">
-        <v>-17.35399752653191</v>
+        <v>-19.37253764460692</v>
       </c>
       <c r="F39">
-        <v>-3.432258783558994</v>
+        <v>-3.977389364124237</v>
       </c>
       <c r="G39">
-        <v>-7.46464902752686</v>
+        <v>-9.059083901787266</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.479635894462622</v>
       </c>
       <c r="E40">
-        <v>-17.33951093818137</v>
+        <v>-20.18673462881602</v>
       </c>
       <c r="F40">
-        <v>-3.223828039880966</v>
+        <v>-3.647998330036775</v>
       </c>
       <c r="G40">
-        <v>-6.801483855645595</v>
+        <v>-8.473719860624414</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.113978493826713</v>
       </c>
       <c r="E41">
-        <v>-17.11810478699835</v>
+        <v>-19.61881870351408</v>
       </c>
       <c r="F41">
-        <v>-3.7207062686146</v>
+        <v>-3.582295122722939</v>
       </c>
       <c r="G41">
-        <v>-6.961115051003713</v>
+        <v>-8.099985753605011</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.728733636471159</v>
       </c>
       <c r="E42">
-        <v>-17.35988001426787</v>
+        <v>-20.79585061063974</v>
       </c>
       <c r="F42">
-        <v>-3.515044634729718</v>
+        <v>-4.251630215265394</v>
       </c>
       <c r="G42">
-        <v>-6.653356806036445</v>
+        <v>-9.173281170164426</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.311593616244224</v>
       </c>
       <c r="E43">
-        <v>-15.7344431393767</v>
+        <v>-18.54509034545139</v>
       </c>
       <c r="F43">
-        <v>-3.620885284764451</v>
+        <v>-4.365285662139863</v>
       </c>
       <c r="G43">
-        <v>-6.162320138924046</v>
+        <v>-7.75772169248192</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.846093007124643</v>
       </c>
       <c r="E44">
-        <v>-15.28429923759224</v>
+        <v>-18.79195557750553</v>
       </c>
       <c r="F44">
-        <v>-3.714772122549448</v>
+        <v>-3.710884916380002</v>
       </c>
       <c r="G44">
-        <v>-6.252800659057867</v>
+        <v>-7.812156992784156</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.319069239028205</v>
       </c>
       <c r="E45">
-        <v>-16.6116447824545</v>
+        <v>-17.05936595064486</v>
       </c>
       <c r="F45">
-        <v>-3.560093149494393</v>
+        <v>-3.866755628136426</v>
       </c>
       <c r="G45">
-        <v>-6.539219127478992</v>
+        <v>-7.213285925821078</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.719506429828511</v>
       </c>
       <c r="E46">
-        <v>-15.20842918406773</v>
+        <v>-18.22427513285199</v>
       </c>
       <c r="F46">
-        <v>-3.245569154688118</v>
+        <v>-3.602430359731836</v>
       </c>
       <c r="G46">
-        <v>-6.318759968382306</v>
+        <v>-7.504054451080805</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.036650312563545</v>
       </c>
       <c r="E47">
-        <v>-14.76410889985714</v>
+        <v>-18.305162735577</v>
       </c>
       <c r="F47">
-        <v>-3.629605169534861</v>
+        <v>-3.645784309166991</v>
       </c>
       <c r="G47">
-        <v>-6.150504801894387</v>
+        <v>-7.982232959318674</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.266591543893048</v>
       </c>
       <c r="E48">
-        <v>-14.4122736403052</v>
+        <v>-16.39863442208171</v>
       </c>
       <c r="F48">
-        <v>-3.687180798090662</v>
+        <v>-4.160514070979458</v>
       </c>
       <c r="G48">
-        <v>-5.878652733846056</v>
+        <v>-7.603284743074919</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.405865775670868</v>
       </c>
       <c r="E49">
-        <v>-15.15886956452779</v>
+        <v>-17.49933437133408</v>
       </c>
       <c r="F49">
-        <v>-3.968150815666521</v>
+        <v>-4.290738249141255</v>
       </c>
       <c r="G49">
-        <v>-6.494692289975795</v>
+        <v>-8.010260037854144</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.454243117690147</v>
       </c>
       <c r="E50">
-        <v>-13.22658329087687</v>
+        <v>-15.59596240422214</v>
       </c>
       <c r="F50">
-        <v>-3.962496193695444</v>
+        <v>-4.143397377445388</v>
       </c>
       <c r="G50">
-        <v>-5.475779204989988</v>
+        <v>-7.956672237209961</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.414978320285742</v>
       </c>
       <c r="E51">
-        <v>-13.14694101850397</v>
+        <v>-16.81035422191108</v>
       </c>
       <c r="F51">
-        <v>-4.178355309969841</v>
+        <v>-4.808855557906847</v>
       </c>
       <c r="G51">
-        <v>-6.178872866620402</v>
+        <v>-7.343873705163168</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.290868929460236</v>
       </c>
       <c r="E52">
-        <v>-12.79004745348546</v>
+        <v>-15.90017623110942</v>
       </c>
       <c r="F52">
-        <v>-3.911935590492083</v>
+        <v>-3.584261293616957</v>
       </c>
       <c r="G52">
-        <v>-5.798554084523388</v>
+        <v>-7.595064658500909</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.088105024913713</v>
       </c>
       <c r="E53">
-        <v>-12.13580975664931</v>
+        <v>-15.6522649215595</v>
       </c>
       <c r="F53">
-        <v>-3.906052123016225</v>
+        <v>-4.098538907390566</v>
       </c>
       <c r="G53">
-        <v>-5.633232061383264</v>
+        <v>-7.562416058392617</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.814012714451232</v>
       </c>
       <c r="E54">
-        <v>-11.86262050518858</v>
+        <v>-15.71851196781771</v>
       </c>
       <c r="F54">
-        <v>-4.089233051431444</v>
+        <v>-4.307678359465753</v>
       </c>
       <c r="G54">
-        <v>-5.761538874848798</v>
+        <v>-8.153149804420167</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.473683915909643</v>
       </c>
       <c r="E55">
-        <v>-10.92208362463949</v>
+        <v>-13.88176743878062</v>
       </c>
       <c r="F55">
-        <v>-4.197303559395117</v>
+        <v>-4.539650891576788</v>
       </c>
       <c r="G55">
-        <v>-6.392532165179425</v>
+        <v>-7.73610051956494</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.07695439226268</v>
       </c>
       <c r="E56">
-        <v>-9.878465090253805</v>
+        <v>-13.99962097483024</v>
       </c>
       <c r="F56">
-        <v>-4.109855278009339</v>
+        <v>-4.769035648221996</v>
       </c>
       <c r="G56">
-        <v>-5.971530088950308</v>
+        <v>-7.145505816450039</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.631856017617046</v>
       </c>
       <c r="E57">
-        <v>-11.24006401251009</v>
+        <v>-13.57432028145187</v>
       </c>
       <c r="F57">
-        <v>-3.807739619050532</v>
+        <v>-4.502364119503683</v>
       </c>
       <c r="G57">
-        <v>-5.810035056453581</v>
+        <v>-6.929853569476374</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.147848003781539</v>
       </c>
       <c r="E58">
-        <v>-10.77023483421429</v>
+        <v>-14.5775221853191</v>
       </c>
       <c r="F58">
-        <v>-4.206484302586919</v>
+        <v>-4.195162388997442</v>
       </c>
       <c r="G58">
-        <v>-6.19646179507055</v>
+        <v>-7.88750169871243</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.637138402758047</v>
       </c>
       <c r="E59">
-        <v>-10.80111449847259</v>
+        <v>-13.81924279815672</v>
       </c>
       <c r="F59">
-        <v>-4.127032944221153</v>
+        <v>-4.287939048935716</v>
       </c>
       <c r="G59">
-        <v>-6.047944101087766</v>
+        <v>-8.712334051458463</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.107808067220771</v>
       </c>
       <c r="E60">
-        <v>-10.25557829171656</v>
+        <v>-12.73995800248662</v>
       </c>
       <c r="F60">
-        <v>-3.829095893320233</v>
+        <v>-4.174048421732803</v>
       </c>
       <c r="G60">
-        <v>-6.854694254098301</v>
+        <v>-9.140433937323778</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.574145644965976</v>
       </c>
       <c r="E61">
-        <v>-9.806743118920322</v>
+        <v>-14.28664924285841</v>
       </c>
       <c r="F61">
-        <v>-4.237068831225885</v>
+        <v>-4.597754686055389</v>
       </c>
       <c r="G61">
-        <v>-6.460994246931554</v>
+        <v>-7.651198268664792</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.047016827362604</v>
       </c>
       <c r="E62">
-        <v>-8.815623183705556</v>
+        <v>-11.81084646185888</v>
       </c>
       <c r="F62">
-        <v>-4.15300572123436</v>
+        <v>-4.733607355040657</v>
       </c>
       <c r="G62">
-        <v>-5.601652767484157</v>
+        <v>-8.133468611189199</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5388490374666693</v>
       </c>
       <c r="E63">
-        <v>-9.33526557608573</v>
+        <v>-12.68085688821251</v>
       </c>
       <c r="F63">
-        <v>-4.437455140706438</v>
+        <v>-4.18356807799051</v>
       </c>
       <c r="G63">
-        <v>-6.485333377736275</v>
+        <v>-9.196064344565691</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.06373632239269397</v>
       </c>
       <c r="E64">
-        <v>-8.618829288754226</v>
+        <v>-12.46529246849939</v>
       </c>
       <c r="F64">
-        <v>-4.036437839181397</v>
+        <v>-4.593491349731026</v>
       </c>
       <c r="G64">
-        <v>-7.004009789556049</v>
+        <v>-9.266866982014083</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.3685273515816532</v>
       </c>
       <c r="E65">
-        <v>-9.184797970232866</v>
+        <v>-13.46606711029851</v>
       </c>
       <c r="F65">
-        <v>-3.878500391205325</v>
+        <v>-4.747460030683007</v>
       </c>
       <c r="G65">
-        <v>-6.695655646391713</v>
+        <v>-9.058560835592061</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.7440038919710703</v>
       </c>
       <c r="E66">
-        <v>-9.338557776689306</v>
+        <v>-13.35769619882095</v>
       </c>
       <c r="F66">
-        <v>-4.438878892324419</v>
+        <v>-4.41372647497541</v>
       </c>
       <c r="G66">
-        <v>-6.863536721233694</v>
+        <v>-8.679804630989585</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.05446838762909</v>
       </c>
       <c r="E67">
-        <v>-9.711627050863212</v>
+        <v>-13.01160304431073</v>
       </c>
       <c r="F67">
-        <v>-4.235903223672122</v>
+        <v>-4.453922514815178</v>
       </c>
       <c r="G67">
-        <v>-6.375214701463498</v>
+        <v>-9.043663380665341</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.290825084922439</v>
       </c>
       <c r="E68">
-        <v>-9.905432152969482</v>
+        <v>-13.18758407272281</v>
       </c>
       <c r="F68">
-        <v>-4.407219027368869</v>
+        <v>-4.47621951039865</v>
       </c>
       <c r="G68">
-        <v>-7.59783227457174</v>
+        <v>-8.022118411975814</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.447546045189622</v>
       </c>
       <c r="E69">
-        <v>-9.814677005381759</v>
+        <v>-12.57583251902662</v>
       </c>
       <c r="F69">
-        <v>-4.221015596214033</v>
+        <v>-4.913825961541047</v>
       </c>
       <c r="G69">
-        <v>-6.580256649983798</v>
+        <v>-9.063291605167681</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.523445688185677</v>
       </c>
       <c r="E70">
-        <v>-9.146215371687514</v>
+        <v>-12.67992855104094</v>
       </c>
       <c r="F70">
-        <v>-3.951314438079484</v>
+        <v>-4.850855438784301</v>
       </c>
       <c r="G70">
-        <v>-6.977270513235355</v>
+        <v>-9.011448462022694</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.518774294482397</v>
       </c>
       <c r="E71">
-        <v>-10.24700589042004</v>
+        <v>-12.70253016481322</v>
       </c>
       <c r="F71">
-        <v>-4.548203695373119</v>
+        <v>-4.604021410362782</v>
       </c>
       <c r="G71">
-        <v>-6.593032045219846</v>
+        <v>-9.68550532872816</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.440373349566199</v>
       </c>
       <c r="E72">
-        <v>-8.798713861760914</v>
+        <v>-14.23682244335202</v>
       </c>
       <c r="F72">
-        <v>-4.446568576396835</v>
+        <v>-4.770628856372928</v>
       </c>
       <c r="G72">
-        <v>-6.409257041243824</v>
+        <v>-8.512714776531489</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.29602717808696</v>
       </c>
       <c r="E73">
-        <v>-9.863439613496354</v>
+        <v>-12.83914516867662</v>
       </c>
       <c r="F73">
-        <v>-4.410655669205372</v>
+        <v>-4.856134722453419</v>
       </c>
       <c r="G73">
-        <v>-6.813752737414134</v>
+        <v>-7.870180924450962</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.097846959327055</v>
       </c>
       <c r="E74">
-        <v>-9.220889908074</v>
+        <v>-14.42028903929877</v>
       </c>
       <c r="F74">
-        <v>-4.785642388451294</v>
+        <v>-5.106202678354266</v>
       </c>
       <c r="G74">
-        <v>-6.285260558070421</v>
+        <v>-7.915942595440308</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.8574788567489037</v>
       </c>
       <c r="E75">
-        <v>-9.80192482257616</v>
+        <v>-13.41667051582284</v>
       </c>
       <c r="F75">
-        <v>-4.875543038447129</v>
+        <v>-5.434219055707127</v>
       </c>
       <c r="G75">
-        <v>-6.94663472481494</v>
+        <v>-8.802586143950075</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5877493237555724</v>
       </c>
       <c r="E76">
-        <v>-11.07779973186724</v>
+        <v>-15.20317162574483</v>
       </c>
       <c r="F76">
-        <v>-4.819594667719443</v>
+        <v>-5.535140715168505</v>
       </c>
       <c r="G76">
-        <v>-6.352964524894056</v>
+        <v>-9.253409614396947</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3001012782843772</v>
       </c>
       <c r="E77">
-        <v>-10.902901008743</v>
+        <v>-15.41469664664311</v>
       </c>
       <c r="F77">
-        <v>-4.957133191651697</v>
+        <v>-5.522733171173995</v>
       </c>
       <c r="G77">
-        <v>-6.179558149547031</v>
+        <v>-9.125993337681477</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.00359117990191161</v>
       </c>
       <c r="E78">
-        <v>-11.77653421430277</v>
+        <v>-14.49108267346069</v>
       </c>
       <c r="F78">
-        <v>-4.678053327085915</v>
+        <v>-4.958985335719803</v>
       </c>
       <c r="G78">
-        <v>-6.400222562467152</v>
+        <v>-9.880877173728249</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2926725040414132</v>
       </c>
       <c r="E79">
-        <v>-11.84736407625674</v>
+        <v>-15.78243590690999</v>
       </c>
       <c r="F79">
-        <v>-5.164578078397364</v>
+        <v>-5.105467046956544</v>
       </c>
       <c r="G79">
-        <v>-6.380776417969473</v>
+        <v>-8.53151536464901</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5817139966223747</v>
       </c>
       <c r="E80">
-        <v>-12.60927077109926</v>
+        <v>-16.08573498204771</v>
       </c>
       <c r="F80">
-        <v>-4.905036393710358</v>
+        <v>-5.341295111118717</v>
       </c>
       <c r="G80">
-        <v>-6.89716855336715</v>
+        <v>-7.265427018064599</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.8539720243907922</v>
       </c>
       <c r="E81">
-        <v>-13.1160251264536</v>
+        <v>-18.06461019628955</v>
       </c>
       <c r="F81">
-        <v>-5.255168432319373</v>
+        <v>-5.984985253772461</v>
       </c>
       <c r="G81">
-        <v>-7.070641139624961</v>
+        <v>-8.354037018288683</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.101224240319197</v>
       </c>
       <c r="E82">
-        <v>-14.57785276392166</v>
+        <v>-18.11693671344818</v>
       </c>
       <c r="F82">
-        <v>-5.264119538153437</v>
+        <v>-5.637419610599415</v>
       </c>
       <c r="G82">
-        <v>-6.375906605481205</v>
+        <v>-8.284767163424972</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.313807824567836</v>
       </c>
       <c r="E83">
-        <v>-15.22746236032197</v>
+        <v>-18.17086178193152</v>
       </c>
       <c r="F83">
-        <v>-4.872169744847244</v>
+        <v>-6.048917877872835</v>
       </c>
       <c r="G83">
-        <v>-6.288693593794645</v>
+        <v>-7.592833350807441</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.484124731565279</v>
       </c>
       <c r="E84">
-        <v>-15.20716573981959</v>
+        <v>-17.75588148081662</v>
       </c>
       <c r="F84">
-        <v>-5.37134593086418</v>
+        <v>-5.650942875411353</v>
       </c>
       <c r="G84">
-        <v>-6.362601522958874</v>
+        <v>-9.184189417716325</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.605999740621029</v>
       </c>
       <c r="E85">
-        <v>-16.16555839338092</v>
+        <v>-18.22257695509911</v>
       </c>
       <c r="F85">
-        <v>-5.483295726467722</v>
+        <v>-5.64118566326633</v>
       </c>
       <c r="G85">
-        <v>-5.950822626602167</v>
+        <v>-9.072498232312393</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.673790375625073</v>
       </c>
       <c r="E86">
-        <v>-17.79048807918324</v>
+        <v>-20.20535118546155</v>
       </c>
       <c r="F86">
-        <v>-5.527590397216647</v>
+        <v>-6.363410198560801</v>
       </c>
       <c r="G86">
-        <v>-5.320819189387782</v>
+        <v>-9.337984121288708</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.683379386969097</v>
       </c>
       <c r="E87">
-        <v>-18.6533752159228</v>
+        <v>-20.60229457460389</v>
       </c>
       <c r="F87">
-        <v>-5.605294136104726</v>
+        <v>-6.289245250540771</v>
       </c>
       <c r="G87">
-        <v>-4.67158479313577</v>
+        <v>-8.343833916936648</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.629923668173553</v>
       </c>
       <c r="E88">
-        <v>-19.91850405639368</v>
+        <v>-22.51613637362157</v>
       </c>
       <c r="F88">
-        <v>-5.215790376584929</v>
+        <v>-6.116409881018161</v>
       </c>
       <c r="G88">
-        <v>-5.154318612035676</v>
+        <v>-7.77221526085285</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.512041898654889</v>
       </c>
       <c r="E89">
-        <v>-21.097102815526</v>
+        <v>-24.0668624843342</v>
       </c>
       <c r="F89">
-        <v>-5.997011916494308</v>
+        <v>-6.283997640989964</v>
       </c>
       <c r="G89">
-        <v>-7.047910933952324</v>
+        <v>-8.204496365734263</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.32600002449288</v>
       </c>
       <c r="E90">
-        <v>-22.48301511472947</v>
+        <v>-24.09389294568598</v>
       </c>
       <c r="F90">
-        <v>-5.84470533490058</v>
+        <v>-6.598986453482419</v>
       </c>
       <c r="G90">
-        <v>-6.328701536636737</v>
+        <v>-8.311943431756848</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.072211111212798</v>
       </c>
       <c r="E91">
-        <v>-23.9162544957871</v>
+        <v>-26.7428464588428</v>
       </c>
       <c r="F91">
-        <v>-5.660094320043719</v>
+        <v>-6.364528294937101</v>
       </c>
       <c r="G91">
-        <v>-6.549319601919309</v>
+        <v>-7.721633435558325</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.7495406654440271</v>
       </c>
       <c r="E92">
-        <v>-25.04770731202556</v>
+        <v>-27.77328713386617</v>
       </c>
       <c r="F92">
-        <v>-5.555314752972331</v>
+        <v>-5.473065778106941</v>
       </c>
       <c r="G92">
-        <v>-6.457352646838356</v>
+        <v>-8.654230666698714</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.3576239573502603</v>
       </c>
       <c r="E93">
-        <v>-28.5067459549925</v>
+        <v>-27.89473174980387</v>
       </c>
       <c r="F93">
-        <v>-5.640073109860734</v>
+        <v>-5.545579712710124</v>
       </c>
       <c r="G93">
-        <v>-6.277394701869112</v>
+        <v>-9.128102155189993</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.09970809943606322</v>
       </c>
       <c r="E94">
-        <v>-30.04089558660005</v>
+        <v>-32.35685002783983</v>
       </c>
       <c r="F94">
-        <v>-5.819183914073274</v>
+        <v>-5.820975877316593</v>
       </c>
       <c r="G94">
-        <v>-7.327976465483588</v>
+        <v>-8.524536734652226</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.6207921564924829</v>
       </c>
       <c r="E95">
-        <v>-31.05747007421193</v>
+        <v>-32.98629659372099</v>
       </c>
       <c r="F95">
-        <v>-5.721467675384744</v>
+        <v>-5.62157938403319</v>
       </c>
       <c r="G95">
-        <v>-7.595485097784397</v>
+        <v>-9.620966243440069</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.201026026419546</v>
       </c>
       <c r="E96">
-        <v>-34.18983592345055</v>
+        <v>-34.8857536950533</v>
       </c>
       <c r="F96">
-        <v>-5.794661811678609</v>
+        <v>-6.398664680017919</v>
       </c>
       <c r="G96">
-        <v>-7.869075202240846</v>
+        <v>-8.237724311311927</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.826168924620313</v>
       </c>
       <c r="E97">
-        <v>-36.16540535166678</v>
+        <v>-37.71117504757802</v>
       </c>
       <c r="F97">
-        <v>-5.74813886670666</v>
+        <v>-6.38246138887058</v>
       </c>
       <c r="G97">
-        <v>-8.098025910645763</v>
+        <v>-8.354305172477362</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.49576046531478</v>
       </c>
       <c r="E98">
-        <v>-37.73163922161869</v>
+        <v>-38.68821595710294</v>
       </c>
       <c r="F98">
-        <v>-6.002851832057491</v>
+        <v>-5.872283197859085</v>
       </c>
       <c r="G98">
-        <v>-8.576101791971915</v>
+        <v>-10.25132059848162</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.172835619843679</v>
       </c>
       <c r="E99">
-        <v>-41.17294662460859</v>
+        <v>-42.5816122414636</v>
       </c>
       <c r="F99">
-        <v>-5.543557320256108</v>
+        <v>-5.824900300575052</v>
       </c>
       <c r="G99">
-        <v>-7.991750777744079</v>
+        <v>-9.813050716719662</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.872551220501982</v>
       </c>
       <c r="E100">
-        <v>-42.67325044148281</v>
+        <v>-42.30521456616843</v>
       </c>
       <c r="F100">
-        <v>-5.716722100609131</v>
+        <v>-6.077311349377791</v>
       </c>
       <c r="G100">
-        <v>-9.859265932447888</v>
+        <v>-10.35292124108185</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.522387867062903</v>
       </c>
       <c r="E101">
-        <v>-45.13295676162208</v>
+        <v>-45.98162901845157</v>
       </c>
       <c r="F101">
-        <v>-5.925994583981215</v>
+        <v>-5.265539330506629</v>
       </c>
       <c r="G101">
-        <v>-9.724847851916859</v>
+        <v>-10.75339131387641</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.184706017336477</v>
       </c>
       <c r="E102">
-        <v>-47.67732290333475</v>
+        <v>-48.3178076246096</v>
       </c>
       <c r="F102">
-        <v>-5.579885158397416</v>
+        <v>-5.441747993629125</v>
       </c>
       <c r="G102">
-        <v>-9.238972325300185</v>
+        <v>-11.50741109753743</v>
       </c>
     </row>
   </sheetData>
